--- a/Luban/Config/Datas/Levels/L06/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L06/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L6 W1/25; N=36; EHP=205.920000; normal:17x18,normal:18x18</t>
+          <t>L6 W1/25; N=36; EHP=391.228053; normal:17x18,normal:18x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L6 W2/25; N=42; EHP=251.555304; normal:17x21,normal:18x21</t>
+          <t>L6 W2/25; N=42; EHP=477.930709; normal:17x21,normal:18x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3304136,3304673,3304019,3304136,3304673,3304091,3304136,3304673,3304099,3304136,3304673,3304099,3304136,3304673,3304107,3304136,3304673,3304115,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304136,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144</t>
+          <t>3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304136,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304144,3304136,3304136,3304136,3304136,3304136,3304136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L6 W3/25; N=48; EHP=318.050304; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x15,normal:18x14,swarm:84x13</t>
+          <t>L6 W3/25; N=48; EHP=653.930365; normal:17x21,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3306136,3306673,3306019,3306136,3306673,3306019,3306136,3306673,3306091,3306136,3306673,3306099,3306136,3306673,3306107,3306136,3306673,3306115,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144</t>
+          <t>3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144,3306144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L6 W4/25; N=54; EHP=412.015032; air:2x2,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x16,normal:18x17,swarm:84x15</t>
+          <t>L6 W4/25; N=54; EHP=839.624788; normal:17x16,normal:18x23,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3308136,3308673,3308019,3308668,3308136,3308673,3308091,3308668,3308136,3308673,3308091,3308668,3308136,3308673,3308099,3308868,3308136,3308673,3308107,3308868,3308136,3308673,3308107,3308868,3308136,3308673,3308115,3308988,3308136,3308673,3308988,3308136,3308673,3308988,3308136,3308673,3308136,3308673,3308136,3308673,3308136,3308673,3308136,3308673,3308144,3308673,3308144,3308673,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144</t>
+          <t>3308136,3308019,3308019,3308668,3308136,3308091,3308091,3308668,3308136,3308091,3308091,3308668,3308136,3308099,3308099,3308868,3308136,3308107,3308107,3308868,3308136,3308107,3308107,3308868,3308136,3308115,3308115,3308988,3308136,3308673,3308988,3308136,3308673,3308988,3308136,3308673,3308136,3308673,3308136,3308673,3308136,3308673,3308136,3308673,3308144,3308673,3308144,3308673,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144,3308144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L6 W5/25; N=60; EHP=788.486899; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x14,normal:18x14,medium:83x3,swarm:84x16,medium:108x3,medium:123x3</t>
+          <t>L6 W5/25; N=60; EHP=1516.494359; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x3,medium:108x3,medium:123x3,normal:17x14,normal:18x14,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3310136,3310673,3310242,3310019,3310668,3310136,3310673,3310242,3310091,3310668,3310136,3310673,3310242,3310091,3310668,3310136,3310673,3310242,3310099,3310868,3310136,3310673,3310786,3310099,3310868,3310136,3310673,3310786,3310107,3310868,3310136,3310673,3310786,3310115,3310988,3310136,3310673,3310115,3310988,3310136,3310673,3310988,3310136,3310673,3310136,3310673,3310136,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310144,3310144,3310144,3310144,3310144</t>
+          <t>3310136,3310019,3310242,3310019,3310668,3310136,3310091,3310242,3310091,3310668,3310136,3310091,3310242,3310091,3310668,3310136,3310099,3310242,3310099,3310868,3310136,3310099,3310786,3310099,3310868,3310136,3310107,3310786,3310107,3310868,3310136,3310115,3310786,3310115,3310988,3310136,3310115,3310115,3310988,3310136,3310673,3310988,3310136,3310673,3310136,3310673,3310136,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310673,3310144,3310144,3310144,3310144,3310144,3310144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L6 W6/25; N=66; EHP=805.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x12,fast:30x4,medium:83x3,swarm:84x18,fast:98x3,medium:108x3,medium:123x3</t>
+          <t>L6 W6/25; N=66; EHP=1549.629082; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x4,fast:98x3,medium:83x3,medium:108x3,medium:123x3,normal:17x12,normal:18x12,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3312136,3312673,3312242,3312019,3312668,3312136,3312673,3312242,3312019,3312668,3312136,3312673,3312242,3312091,3312668,3312136,3312673,3312242,3312099,3312868,3312136,3312673,3312786,3312099,3312868,3312136,3312673,3312786,3312107,3312868,3312136,3312673,3312786,3312107,3312988,3312136,3312673,3312786,3312115,3312988,3312136,3312673,3312115,3312988,3312136,3312673,3312988,3312136,3312673,3312136,3312673,3312136,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312144,3312144,3312144,3312144</t>
+          <t>3312136,3312019,3312242,3312019,3312668,3312136,3312019,3312242,3312019,3312668,3312136,3312091,3312242,3312091,3312668,3312136,3312099,3312242,3312099,3312868,3312136,3312099,3312786,3312099,3312868,3312136,3312107,3312786,3312107,3312868,3312136,3312107,3312786,3312107,3312988,3312136,3312115,3312786,3312115,3312988,3312136,3312115,3312115,3312988,3312136,3312673,3312988,3312136,3312673,3312136,3312673,3312136,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312673,3312144,3312144,3312144,3312144,3312144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L6 W7/25; N=72; EHP=924.827904; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x12,fast:30x4,medium:83x3,swarm:84x20,fast:98x4,medium:108x3,medium:123x4</t>
+          <t>L6 W7/25; N=72; EHP=1781.098237; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x4,fast:98x4,medium:83x3,medium:108x3,medium:123x4,normal:17x13,normal:18x12,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3314136,3314673,3314242,3314019,3314668,3314136,3314673,3314242,3314019,3314668,3314136,3314673,3314242,3314091,3314668,3314136,3314673,3314242,3314091,3314668,3314136,3314673,3314242,3314099,3314868,3314136,3314673,3314786,3314099,3314868,3314136,3314673,3314786,3314107,3314868,3314136,3314673,3314786,3314107,3314868,3314136,3314673,3314786,3314115,3314988,3314136,3314673,3314988,3314136,3314673,3314988,3314136,3314673,3314136,3314673,3314136,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314144,3314144,3314144,3314144,3314144,3314144</t>
+          <t>3314136,3314019,3314242,3314019,3314668,3314136,3314019,3314242,3314019,3314668,3314136,3314091,3314242,3314091,3314668,3314136,3314091,3314242,3314091,3314668,3314136,3314099,3314242,3314099,3314868,3314136,3314099,3314786,3314099,3314868,3314136,3314107,3314786,3314107,3314868,3314136,3314107,3314786,3314107,3314868,3314136,3314115,3314786,3314115,3314988,3314136,3314673,3314988,3314136,3314673,3314988,3314136,3314673,3314136,3314673,3314136,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314673,3314144,3314144,3314144,3314144,3314144,3314144,3314144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L6 W8/25; N=78; EHP=1194.771864; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x14,normal:18x14,fast:30x5,medium:83x4,swarm:84x21,fast:98x4,medium:108x4,medium:123x3</t>
+          <t>L6 W8/25; N=78; EHP=2298.305498; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,fast:30x5,fast:98x4,medium:83x4,medium:108x4,medium:123x3,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3316136,3316673,3316242,3316019,3316668,3316136,3316673,3316242,3316019,3316668,3316136,3316673,3316242,3316091,3316668,3316136,3316673,3316242,3316091,3316668,3316136,3316673,3316242,3316099,3316868,3316136,3316673,3316786,3316099,3316868,3316136,3316673,3316786,3316107,3316868,3316136,3316673,3316786,3316107,3316868,3316136,3316673,3316786,3316115,3316988,3316136,3316673,3316786,3316115,3316988,3316136,3316673,3316988,3316136,3316673,3316988,3316136,3316673,3316136,3316673,3316136,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316144,3316144,3316144,3316144,3316144</t>
+          <t>3316136,3316019,3316242,3316019,3316668,3316136,3316019,3316242,3316019,3316668,3316136,3316091,3316242,3316091,3316668,3316136,3316091,3316242,3316091,3316668,3316136,3316099,3316242,3316099,3316868,3316136,3316099,3316786,3316099,3316868,3316136,3316107,3316786,3316107,3316868,3316136,3316107,3316786,3316107,3316868,3316136,3316115,3316786,3316115,3316988,3316136,3316115,3316786,3316115,3316988,3316136,3316673,3316988,3316136,3316673,3316988,3316136,3316673,3316136,3316673,3316136,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316673,3316144,3316144,3316144,3316144,3316144,3316144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L6 W9/25; N=84; EHP=1526.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x5,medium:83x4,swarm:84x23,fast:98x5,medium:108x4,medium:123x4</t>
+          <t>L6 W9/25; N=84; EHP=2936.734428; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x5,fast:98x5,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3318136,3318673,3318242,3318019,3318668,3318136,3318673,3318242,3318019,3318668,3318136,3318673,3318242,3318091,3318668,3318136,3318673,3318242,3318091,3318668,3318136,3318673,3318242,3318099,3318868,3318136,3318673,3318786,3318099,3318868,3318136,3318673,3318786,3318107,3318868,3318136,3318673,3318786,3318107,3318868,3318136,3318673,3318786,3318107,3318988,3318136,3318673,3318786,3318115,3318988,3318136,3318673,3318115,3318988,3318136,3318673,3318988,3318136,3318673,3318988,3318136,3318673,3318136,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318144,3318144,3318144,3318144,3318144</t>
+          <t>3318136,3318019,3318242,3318019,3318668,3318136,3318019,3318242,3318019,3318668,3318136,3318091,3318242,3318091,3318668,3318136,3318091,3318242,3318091,3318668,3318136,3318099,3318242,3318099,3318868,3318136,3318099,3318786,3318099,3318868,3318136,3318107,3318786,3318107,3318868,3318136,3318107,3318786,3318107,3318868,3318136,3318107,3318786,3318107,3318988,3318136,3318115,3318786,3318115,3318988,3318136,3318115,3318115,3318988,3318136,3318673,3318988,3318136,3318673,3318988,3318136,3318673,3318136,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318673,3318144,3318144,3318144,3318144,3318144,3318144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L6 W10/25; N=90; EHP=2819.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x15,normal:18x16,fast:30x5,medium:83x4,swarm:84x25,fast:98x5,medium:108x4,medium:123x5</t>
+          <t>L6 W10/25; N=90; EHP=5426.979214; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x5,fast:98x5,medium:83x4,medium:108x4,medium:123x5,normal:17x15,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3320136,3320673,3320242,3320019,3320668,3320253,3320136,3320673,3320242,3320019,3320668,3320253,3320136,3320673,3320242,3320091,3320668,3320325,3320136,3320673,3320242,3320091,3320668,3320325,3320136,3320673,3320242,3320091,3320668,3320645,3320136,3320673,3320786,3320099,3320868,3320693,3320136,3320673,3320786,3320099,3320868,3320693,3320136,3320673,3320786,3320107,3320868,3320709,3320136,3320673,3320786,3320107,3320868,3320709,3320136,3320673,3320786,3320115,3320868,3320136,3320673,3320786,3320115,3320988,3320136,3320673,3320115,3320988,3320144,3320673,3320988,3320144,3320673,3320988,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320673,3320673</t>
+          <t>3320136,3320019,3320242,3320019,3320668,3320253,3320136,3320019,3320242,3320019,3320668,3320253,3320136,3320091,3320242,3320091,3320668,3320325,3320136,3320091,3320242,3320091,3320668,3320325,3320136,3320091,3320242,3320091,3320668,3320645,3320136,3320099,3320786,3320099,3320868,3320693,3320136,3320099,3320786,3320099,3320868,3320693,3320136,3320107,3320786,3320107,3320868,3320709,3320136,3320107,3320786,3320107,3320868,3320709,3320136,3320115,3320786,3320115,3320868,3320136,3320115,3320786,3320115,3320988,3320136,3320115,3320115,3320988,3320144,3320673,3320988,3320144,3320673,3320988,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320144,3320673,3320673,3320673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L6 W11/25; N=96; EHP=2876.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x12,normal:18x12,fast:30x5,heavy:31x2,heavy:40x2,heavy:80x1,medium:83x5,swarm:84x26,heavy:86x2,heavy:88x2,fast:98x6,medium:108x5,medium:123x4</t>
+          <t>L6 W11/25; N=96; EHP=5530.186346; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x1,heavy:86x2,heavy:88x2,medium:83x5,medium:108x5,medium:123x4,normal:17x12,normal:18x12,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3322136,3322673,3322242,3322019,3322668,3322253,3322136,3322673,3322242,3322019,3322668,3322253,3322136,3322673,3322242,3322091,3322668,3322325,3322136,3322673,3322242,3322091,3322668,3322325,3322136,3322673,3322242,3322099,3322668,3322645,3322136,3322673,3322242,3322099,3322868,3322645,3322136,3322673,3322786,3322099,3322868,3322693,3322136,3322673,3322786,3322107,3322868,3322693,3322136,3322673,3322786,3322107,3322868,3322709,3322136,3322673,3322786,3322115,3322868,3322709,3322136,3322673,3322786,3322115,3322988,3322136,3322673,3322786,3322115,3322988,3322144,3322673,3322988,3322144,3322673,3322988,3322144,3322673,3322988,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322673,3322673,3322673</t>
+          <t>3322136,3322019,3322242,3322019,3322668,3322253,3322136,3322019,3322242,3322019,3322668,3322253,3322136,3322091,3322242,3322091,3322668,3322325,3322136,3322091,3322242,3322091,3322668,3322325,3322136,3322099,3322242,3322099,3322668,3322645,3322136,3322099,3322242,3322099,3322868,3322645,3322136,3322099,3322786,3322099,3322868,3322693,3322136,3322107,3322786,3322107,3322868,3322693,3322136,3322107,3322786,3322107,3322868,3322709,3322136,3322115,3322786,3322115,3322868,3322709,3322136,3322115,3322786,3322115,3322988,3322136,3322115,3322786,3322115,3322988,3322144,3322673,3322988,3322144,3322673,3322988,3322144,3322673,3322988,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322144,3322673,3322673,3322673,3322673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L6 W12/25; N=102; EHP=2977.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x12,normal:18x13,fast:30x6,heavy:31x2,heavy:40x2,heavy:80x2,medium:83x5,swarm:84x28,heavy:86x2,heavy:88x2,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L6 W12/25; N=102; EHP=5719.861232; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,medium:83x5,medium:108x5,medium:123x5,normal:17x12,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3324136,3324673,3324242,3324019,3324668,3324253,3324136,3324673,3324242,3324019,3324668,3324253,3324136,3324673,3324242,3324019,3324668,3324325,3324136,3324673,3324242,3324091,3324668,3324325,3324136,3324673,3324242,3324091,3324668,3324645,3324136,3324673,3324242,3324099,3324868,3324645,3324136,3324673,3324786,3324099,3324868,3324693,3324136,3324673,3324786,3324099,3324868,3324693,3324136,3324673,3324786,3324107,3324868,3324709,3324136,3324673,3324786,3324107,3324868,3324709,3324136,3324673,3324786,3324107,3324988,3324136,3324673,3324786,3324115,3324988,3324136,3324673,3324115,3324988,3324136,3324673,3324988,3324144,3324673,3324988,3324144,3324673,3324988,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324673,3324673,3324673</t>
+          <t>3324136,3324019,3324242,3324019,3324668,3324253,3324136,3324019,3324242,3324019,3324668,3324253,3324136,3324019,3324242,3324019,3324668,3324325,3324136,3324091,3324242,3324091,3324668,3324325,3324136,3324091,3324242,3324091,3324668,3324645,3324136,3324099,3324242,3324099,3324868,3324645,3324136,3324099,3324786,3324099,3324868,3324693,3324136,3324099,3324786,3324099,3324868,3324693,3324136,3324107,3324786,3324107,3324868,3324709,3324136,3324107,3324786,3324107,3324868,3324709,3324136,3324107,3324786,3324107,3324988,3324136,3324115,3324786,3324115,3324988,3324136,3324115,3324115,3324988,3324136,3324673,3324988,3324144,3324673,3324988,3324144,3324673,3324988,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673,3324673,3324673,3324673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L6 W13/25; N=108; EHP=3632.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x13,fast:30x6,heavy:31x2,heavy:40x2,heavy:80x2,medium:83x5,swarm:84x30,heavy:86x2,heavy:88x2,fast:98x6,medium:108x5,medium:123x6</t>
+          <t>L6 W13/25; N=108; EHP=6980.721838; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3326136,3326673,3326242,3326019,3326668,3326253,3326136,3326673,3326242,3326019,3326668,3326253,3326136,3326673,3326242,3326019,3326668,3326325,3326136,3326673,3326242,3326091,3326668,3326325,3326136,3326673,3326242,3326091,3326668,3326645,3326136,3326673,3326242,3326091,3326668,3326645,3326136,3326673,3326242,3326099,3326868,3326693,3326136,3326673,3326786,3326099,3326868,3326693,3326136,3326673,3326786,3326107,3326868,3326709,3326136,3326673,3326786,3326107,3326868,3326709,3326136,3326673,3326786,3326107,3326868,3326709,3326136,3326673,3326786,3326115,3326868,3326136,3326673,3326786,3326115,3326988,3326136,3326673,3326115,3326988,3326144,3326673,3326988,3326144,3326673,3326988,3326144,3326673,3326988,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326673,3326673,3326673</t>
+          <t>3326136,3326019,3326242,3326019,3326668,3326253,3326136,3326019,3326242,3326019,3326668,3326253,3326136,3326019,3326242,3326019,3326668,3326325,3326136,3326091,3326242,3326091,3326668,3326325,3326136,3326091,3326242,3326091,3326668,3326645,3326136,3326091,3326242,3326091,3326668,3326645,3326136,3326099,3326242,3326099,3326868,3326693,3326136,3326099,3326786,3326099,3326868,3326693,3326136,3326107,3326786,3326107,3326868,3326709,3326136,3326107,3326786,3326107,3326868,3326709,3326136,3326107,3326786,3326107,3326868,3326709,3326136,3326115,3326786,3326115,3326868,3326136,3326115,3326786,3326115,3326988,3326136,3326115,3326115,3326988,3326144,3326673,3326988,3326144,3326673,3326988,3326144,3326673,3326988,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326673,3326673,3326673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L6 W14/25; N=114; EHP=4384.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x7,heavy:31x2,heavy:40x2,heavy:80x2,medium:83x6,swarm:84x31,heavy:86x2,heavy:88x3,fast:98x6,medium:108x6,medium:123x5</t>
+          <t>L6 W14/25; N=114; EHP=8427.496110; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x7,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x3,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3328136,3328673,3328242,3328019,3328668,3328253,3328326,3328136,3328673,3328242,3328019,3328668,3328253,3328136,3328673,3328242,3328091,3328668,3328325,3328136,3328673,3328242,3328091,3328668,3328325,3328136,3328673,3328242,3328091,3328668,3328645,3328136,3328673,3328242,3328099,3328668,3328645,3328136,3328673,3328242,3328099,3328868,3328645,3328136,3328673,3328786,3328099,3328868,3328693,3328136,3328673,3328786,3328107,3328868,3328693,3328136,3328673,3328786,3328107,3328868,3328693,3328136,3328673,3328786,3328107,3328868,3328709,3328136,3328673,3328786,3328115,3328868,3328709,3328136,3328673,3328786,3328115,3328988,3328136,3328673,3328786,3328115,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328673,3328673,3328673,3328673,3328673</t>
+          <t>3328136,3328019,3328242,3328019,3328668,3328253,3328326,3328136,3328019,3328242,3328019,3328668,3328253,3328136,3328091,3328242,3328091,3328668,3328325,3328136,3328091,3328242,3328091,3328668,3328325,3328136,3328091,3328242,3328091,3328668,3328645,3328136,3328099,3328242,3328099,3328668,3328645,3328136,3328099,3328242,3328099,3328868,3328645,3328136,3328099,3328786,3328099,3328868,3328693,3328136,3328107,3328786,3328107,3328868,3328693,3328136,3328107,3328786,3328107,3328868,3328693,3328136,3328107,3328786,3328107,3328868,3328709,3328136,3328115,3328786,3328115,3328868,3328709,3328136,3328115,3328786,3328115,3328988,3328136,3328115,3328786,3328115,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328988,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328144,3328673,3328673,3328673,3328673,3328673,3328673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L6 W15/25; N=120; EHP=7652.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x7,heavy:31x2,elite:40x1,heavy:40x2,heavy:80x3,medium:83x6,swarm:84x33,heavy:86x3,heavy:88x2,fast:98x7,medium:108x6,medium:123x6</t>
+          <t>L6 W15/25; N=120; EHP=14695.287660; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,elite:40x1,fast:30x7,fast:98x7,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x3,heavy:88x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3330136,3330673,3330242,3330019,3330668,3330253,3330136,3330673,3330242,3330019,3330668,3330253,3330136,3330673,3330242,3330019,3330668,3330253,3330136,3330673,3330242,3330091,3330668,3330325,3330136,3330673,3330242,3330091,3330668,3330325,3330136,3330673,3330242,3330091,3330668,3330645,3330136,3330673,3330242,3330099,3330868,3330645,3330136,3330673,3330242,3330099,3330868,3330693,3330136,3330673,3330786,3330099,3330868,3330693,3330136,3330673,3330786,3330107,3330868,3330693,3330136,3330673,3330786,3330107,3330868,3330709,3330136,3330673,3330786,3330107,3330868,3330709,3330136,3330673,3330786,3330115,3330988,3330136,3330673,3330786,3330115,3330988,3330136,3330673,3330786,3330115,3330988,3330144,3330673,3330988,3330144,3330673,3330988,3330144,3330673,3330988,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330673,3330673,3330673,3330673</t>
+          <t>3330136,3330019,3330242,3330019,3330668,3330253,3330136,3330019,3330242,3330019,3330668,3330253,3330136,3330019,3330242,3330019,3330668,3330253,3330136,3330091,3330242,3330091,3330668,3330325,3330136,3330091,3330242,3330091,3330668,3330325,3330136,3330091,3330242,3330091,3330668,3330645,3330136,3330099,3330242,3330099,3330868,3330645,3330136,3330099,3330242,3330099,3330868,3330693,3330136,3330099,3330786,3330099,3330868,3330693,3330136,3330107,3330786,3330107,3330868,3330693,3330136,3330107,3330786,3330107,3330868,3330709,3330136,3330107,3330786,3330107,3330868,3330709,3330136,3330115,3330786,3330115,3330988,3330136,3330115,3330786,3330115,3330988,3330136,3330115,3330786,3330115,3330988,3330144,3330673,3330988,3330144,3330673,3330988,3330144,3330673,3330988,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330144,3330673,3330673,3330673,3330673,3330673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L6 W16/25; N=126; EHP=7806.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x8,heavy:31x3,heavy:40x2,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x3,heavy:88x2,fast:98x7,medium:108x6,medium:123x6</t>
+          <t>L6 W16/25; N=126; EHP=15001.438196; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x8,fast:98x7,heavy:31x3,heavy:40x2,heavy:80x2,heavy:86x3,heavy:88x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3332136,3332673,3332242,3332019,3332668,3332253,3332136,3332673,3332242,3332019,3332668,3332253,3332136,3332673,3332242,3332019,3332668,3332253,3332136,3332673,3332242,3332091,3332668,3332325,3332136,3332673,3332242,3332091,3332668,3332325,3332136,3332673,3332242,3332091,3332668,3332325,3332136,3332673,3332242,3332099,3332868,3332645,3332136,3332673,3332786,3332099,3332868,3332645,3332136,3332673,3332786,3332099,3332868,3332693,3332136,3332673,3332786,3332107,3332868,3332693,3332136,3332673,3332786,3332107,3332868,3332709,3332136,3332673,3332786,3332107,3332868,3332709,3332136,3332673,3332786,3332115,3332868,3332709,3332136,3332673,3332786,3332115,3332988,3332136,3332673,3332786,3332115,3332988,3332136,3332673,3332115,3332988,3332136,3332673,3332988,3332144,3332673,3332988,3332144,3332673,3332988,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332673,3332673,3332673</t>
+          <t>3332136,3332019,3332242,3332019,3332668,3332253,3332136,3332019,3332242,3332019,3332668,3332253,3332136,3332019,3332242,3332019,3332668,3332253,3332136,3332091,3332242,3332091,3332668,3332325,3332136,3332091,3332242,3332091,3332668,3332325,3332136,3332091,3332242,3332091,3332668,3332325,3332136,3332099,3332242,3332099,3332868,3332645,3332136,3332099,3332786,3332099,3332868,3332645,3332136,3332099,3332786,3332099,3332868,3332693,3332136,3332107,3332786,3332107,3332868,3332693,3332136,3332107,3332786,3332107,3332868,3332709,3332136,3332107,3332786,3332107,3332868,3332709,3332136,3332115,3332786,3332115,3332868,3332709,3332136,3332115,3332786,3332115,3332988,3332136,3332115,3332786,3332115,3332988,3332136,3332115,3332115,3332988,3332136,3332673,3332988,3332144,3332673,3332988,3332144,3332673,3332988,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332673,3332673,3332673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L6 W17/25; N=132; EHP=7963.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x16,fast:30x7,heavy:31x3,heavy:40x3,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x3,fast:98x8,medium:108x7,medium:123x6</t>
+          <t>L6 W17/25; N=132; EHP=15305.295006; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x7,fast:98x8,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x3,medium:83x6,medium:108x7,medium:123x6,normal:17x17,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3334136,3334673,3334242,3334019,3334668,3334253,3334136,3334673,3334242,3334019,3334668,3334253,3334136,3334673,3334242,3334019,3334668,3334325,3334136,3334673,3334242,3334019,3334668,3334325,3334136,3334673,3334242,3334091,3334668,3334325,3334136,3334673,3334242,3334091,3334668,3334645,3334136,3334673,3334242,3334091,3334668,3334645,3334136,3334673,3334242,3334099,3334868,3334645,3334136,3334673,3334786,3334099,3334868,3334693,3334136,3334673,3334786,3334099,3334868,3334693,3334136,3334673,3334786,3334099,3334868,3334709,3334136,3334673,3334786,3334107,3334868,3334709,3334136,3334673,3334786,3334107,3334868,3334709,3334136,3334673,3334786,3334107,3334988,3334136,3334673,3334786,3334115,3334988,3334136,3334673,3334786,3334115,3334988,3334136,3334673,3334115,3334988,3334144,3334673,3334988,3334144,3334673,3334988,3334144,3334673,3334988,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334673,3334673,3334673,3334673</t>
+          <t>3334136,3334019,3334242,3334019,3334668,3334253,3334136,3334019,3334242,3334019,3334668,3334253,3334136,3334019,3334242,3334019,3334668,3334325,3334136,3334019,3334242,3334019,3334668,3334325,3334136,3334091,3334242,3334091,3334668,3334325,3334136,3334091,3334242,3334091,3334668,3334645,3334136,3334091,3334242,3334091,3334668,3334645,3334136,3334099,3334242,3334099,3334868,3334645,3334136,3334099,3334786,3334099,3334868,3334693,3334136,3334099,3334786,3334099,3334868,3334693,3334136,3334099,3334786,3334099,3334868,3334709,3334136,3334107,3334786,3334107,3334868,3334709,3334136,3334107,3334786,3334107,3334868,3334709,3334136,3334107,3334786,3334107,3334988,3334136,3334115,3334786,3334115,3334988,3334136,3334115,3334786,3334115,3334988,3334136,3334115,3334115,3334988,3334144,3334673,3334988,3334144,3334673,3334988,3334144,3334673,3334988,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334673,3334673,3334673,3334673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L6 W18/25; N=138; EHP=8509.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x8,heavy:31x2,heavy:40x3,heavy:80x3,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x3,fast:98x8,medium:108x6,medium:123x7</t>
+          <t>L6 W18/25; N=138; EHP=16359.068920; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x8,fast:98x8,heavy:31x2,heavy:40x3,heavy:80x3,heavy:86x2,heavy:88x3,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3336136,3336673,3336242,3336019,3336668,3336253,3336136,3336673,3336242,3336019,3336668,3336253,3336136,3336673,3336242,3336019,3336668,3336253,3336136,3336673,3336242,3336019,3336668,3336325,3336136,3336673,3336242,3336091,3336668,3336325,3336136,3336673,3336242,3336091,3336668,3336645,3336136,3336673,3336242,3336091,3336668,3336645,3336136,3336673,3336242,3336099,3336868,3336645,3336136,3336673,3336786,3336099,3336868,3336693,3336136,3336673,3336786,3336099,3336868,3336693,3336136,3336673,3336786,3336107,3336868,3336693,3336136,3336673,3336786,3336107,3336868,3336709,3336136,3336673,3336786,3336107,3336868,3336709,3336136,3336673,3336786,3336107,3336868,3336709,3336136,3336673,3336786,3336115,3336988,3336136,3336673,3336786,3336115,3336988,3336136,3336673,3336786,3336115,3336988,3336136,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336673,3336673,3336673,3336673,3336673</t>
+          <t>3336136,3336019,3336242,3336019,3336668,3336253,3336136,3336019,3336242,3336019,3336668,3336253,3336136,3336019,3336242,3336019,3336668,3336253,3336136,3336019,3336242,3336019,3336668,3336325,3336136,3336091,3336242,3336091,3336668,3336325,3336136,3336091,3336242,3336091,3336668,3336645,3336136,3336091,3336242,3336091,3336668,3336645,3336136,3336099,3336242,3336099,3336868,3336645,3336136,3336099,3336786,3336099,3336868,3336693,3336136,3336099,3336786,3336099,3336868,3336693,3336136,3336107,3336786,3336107,3336868,3336693,3336136,3336107,3336786,3336107,3336868,3336709,3336136,3336107,3336786,3336107,3336868,3336709,3336136,3336107,3336786,3336107,3336868,3336709,3336136,3336115,3336786,3336115,3336988,3336136,3336115,3336786,3336115,3336988,3336136,3336115,3336786,3336115,3336988,3336136,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336988,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336673,3336673,3336673,3336673,3336673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L6 W19/25; N=144; EHP=9854.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x17,fast:30x8,heavy:31x3,heavy:40x2,heavy:80x3,medium:83x7,swarm:84x40,heavy:86x3,heavy:88x3,fast:98x9,medium:108x7,medium:123x7</t>
+          <t>L6 W19/25; N=144; EHP=18934.391415; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x8,fast:98x9,heavy:31x3,heavy:40x2,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3338136,3338673,3338242,3338019,3338668,3338253,3338326,3338136,3338673,3338242,3338019,3338668,3338253,3338136,3338673,3338242,3338019,3338668,3338253,3338136,3338673,3338242,3338091,3338668,3338325,3338136,3338673,3338242,3338091,3338668,3338325,3338136,3338673,3338242,3338091,3338668,3338325,3338136,3338673,3338242,3338091,3338668,3338645,3338136,3338673,3338242,3338099,3338868,3338645,3338136,3338673,3338242,3338099,3338868,3338645,3338136,3338673,3338786,3338099,3338868,3338693,3338136,3338673,3338786,3338107,3338868,3338693,3338136,3338673,3338786,3338107,3338868,3338693,3338136,3338673,3338786,3338107,3338868,3338709,3338136,3338673,3338786,3338107,3338868,3338709,3338136,3338673,3338786,3338115,3338868,3338709,3338136,3338673,3338786,3338115,3338988,3338136,3338673,3338786,3338115,3338988,3338144,3338673,3338786,3338115,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338673,3338673,3338673,3338673,3338673,3338673,3338673,3338673</t>
+          <t>3338136,3338019,3338242,3338019,3338668,3338253,3338326,3338136,3338019,3338242,3338019,3338668,3338253,3338136,3338019,3338242,3338019,3338668,3338253,3338136,3338091,3338242,3338091,3338668,3338325,3338136,3338091,3338242,3338091,3338668,3338325,3338136,3338091,3338242,3338091,3338668,3338325,3338136,3338091,3338242,3338091,3338668,3338645,3338136,3338099,3338242,3338099,3338868,3338645,3338136,3338099,3338242,3338099,3338868,3338645,3338136,3338099,3338786,3338099,3338868,3338693,3338136,3338107,3338786,3338107,3338868,3338693,3338136,3338107,3338786,3338107,3338868,3338693,3338136,3338107,3338786,3338107,3338868,3338709,3338136,3338107,3338786,3338107,3338868,3338709,3338136,3338115,3338786,3338115,3338868,3338709,3338136,3338115,3338786,3338115,3338988,3338136,3338115,3338786,3338115,3338988,3338144,3338115,3338786,3338115,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338988,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338673,3338673,3338673,3338673,3338673,3338673,3338673,3338673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L6 W20/25; N=150; EHP=16551.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x17,normal:18x17,fast:30x9,heavy:31x3,elite:40x1,heavy:40x3,heavy:80x3,medium:83x7,swarm:84x42,heavy:86x3,heavy:88x3,fast:98x9,medium:108x8,medium:123x7</t>
+          <t>L6 W20/25; N=150; EHP=31799.277532; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:40x1,fast:30x9,fast:98x9,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x7,medium:108x8,medium:123x7,normal:17x17,normal:18x17,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017052,10017059,10017054,10048520,10017058,10017055,10017052,10017059,10017054,10048520,10017058,10017055,10017052,10017059,10017054,10048520,10017058,10017055,10017052,10017059,10017054,10048520,10017058,10017056,10017052,10017059,10017054,10017049,10017058,10017056,10017052,10017059,10017054,10017049,10017058,10017056,10017052,10017059,10017054,10017049,10017058,10017057,10017052,10017059,10017054,10017049,10017058,10017057,10017052,10017059,10017054,10048521,10017063,10017057,10017052,10017059,10017062,10048521,10017063,10017060,10017052,10017059,10017062,10048521,10017063,10017060,10017052,10017059,10017062,10048521,10017063,10017060,10017052,10017059,10017062,10017050,10017063,10017061,10017052,10017059,10017062,10017050,10017063,10017061,10017052,10017059,10017062,10017050,10017063,10017061,10017052,10017059,10017062,10017051,10017064,10017052,10017059,10017062,10017051,10017064,10017052,10017059,10017062,10017051,10017064,10017052,10017059,10017051,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017059,10017059,10017059,10017059,10017059</t>
+          <t>10017052,10048520,10017054,10048520,10017058,10017055,10017052,10048520,10017054,10048520,10017058,10017055,10017052,10048520,10017054,10048520,10017058,10017055,10017052,10048520,10017054,10048520,10017058,10017056,10017052,10017049,10017054,10017049,10017058,10017056,10017052,10017049,10017054,10017049,10017058,10017056,10017052,10017049,10017054,10017049,10017058,10017057,10017052,10017049,10017054,10017049,10017058,10017057,10017052,10048521,10017054,10048521,10017063,10017057,10017052,10048521,10017062,10048521,10017063,10017060,10017052,10048521,10017062,10048521,10017063,10017060,10017052,10048521,10017062,10048521,10017063,10017060,10017052,10017050,10017062,10017050,10017063,10017061,10017052,10017050,10017062,10017050,10017063,10017061,10017052,10017050,10017062,10017050,10017063,10017061,10017052,10017051,10017062,10017051,10017064,10017052,10017051,10017062,10017051,10017064,10017052,10017051,10017062,10017051,10017064,10017052,10017051,10017051,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017064,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017053,10017059,10017059,10017059,10017059,10017059,10017059</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L6 W21/25; N=156; EHP=16883.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x19,fast:30x9,heavy:31x3,heavy:40x3,heavy:80x3,medium:83x8,swarm:84x43,heavy:86x3,heavy:88x3,fast:98x9,medium:108x7,medium:123x8</t>
+          <t>L6 W21/25; N=156; EHP=32452.497668; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x9,fast:98x9,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017068,10017075,10017070,10048522,10017074,10017071,10017068,10017075,10017070,10048522,10017074,10017071,10017068,10017075,10017070,10048522,10017074,10017071,10017068,10017075,10017070,10048522,10017074,10017071,10017068,10017075,10017070,10017065,10017074,10017072,10017068,10017075,10017070,10017065,10017074,10017072,10017068,10017075,10017070,10017065,10017074,10017072,10017068,10017075,10017070,10048523,10017074,10017073,10017068,10017075,10017070,10048523,10017079,10017073,10017068,10017075,10017070,10048523,10017079,10017073,10017068,10017075,10017078,10048523,10017079,10017076,10017068,10017075,10017078,10017066,10017079,10017076,10017068,10017075,10017078,10017066,10017079,10017076,10017068,10017075,10017078,10017066,10017079,10017077,10017068,10017075,10017078,10017066,10017079,10017077,10017068,10017075,10017078,10017067,10017079,10017077,10017068,10017075,10017078,10017067,10017080,10017068,10017075,10017078,10017067,10017080,10017068,10017075,10017078,10017067,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017075,10017075,10017075,10017075,10017075,10017075</t>
+          <t>10017068,10048522,10017070,10048522,10017074,10017071,10017068,10048522,10017070,10048522,10017074,10017071,10017068,10048522,10017070,10048522,10017074,10017071,10017068,10048522,10017070,10048522,10017074,10017071,10017068,10017065,10017070,10017065,10017074,10017072,10017068,10017065,10017070,10017065,10017074,10017072,10017068,10017065,10017070,10017065,10017074,10017072,10017068,10048523,10017070,10048523,10017074,10017073,10017068,10048523,10017070,10048523,10017079,10017073,10017068,10048523,10017070,10048523,10017079,10017073,10017068,10048523,10017078,10048523,10017079,10017076,10017068,10017066,10017078,10017066,10017079,10017076,10017068,10017066,10017078,10017066,10017079,10017076,10017068,10017066,10017078,10017066,10017079,10017077,10017068,10017066,10017078,10017066,10017079,10017077,10017068,10017067,10017078,10017067,10017079,10017077,10017068,10017067,10017078,10017067,10017080,10017068,10017067,10017078,10017067,10017080,10017068,10017067,10017078,10017067,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017080,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017069,10017075,10017075,10017075,10017075,10017075,10017075,10017075</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L6 W22/25; N=162; EHP=17221.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x10,heavy:31x4,heavy:40x3,heavy:80x3,medium:83x8,swarm:84x45,heavy:86x3,heavy:88x3,fast:98x9,medium:108x8,medium:123x8</t>
+          <t>L6 W22/25; N=162; EHP=33086.178772; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x9,heavy:31x4,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017084,10017091,10017086,10048524,10017090,10017087,10017084,10017091,10017086,10048524,10017090,10017087,10017084,10017091,10017086,10048524,10017090,10017087,10017084,10017091,10017086,10048524,10017090,10017088,10017084,10017091,10017086,10017081,10017090,10017088,10017084,10017091,10017086,10017081,10017090,10017088,10017084,10017091,10017086,10017081,10017090,10017088,10017084,10017091,10017086,10017081,10017090,10017089,10017084,10017091,10017086,10048525,10017095,10017089,10017084,10017091,10017086,10048525,10017095,10017089,10017084,10017091,10017094,10048525,10017095,10017092,10017084,10017091,10017094,10048525,10017095,10017092,10017084,10017091,10017094,10017082,10017095,10017092,10017084,10017091,10017094,10017082,10017095,10017093,10017084,10017091,10017094,10017082,10017095,10017093,10017084,10017091,10017094,10017082,10017095,10017093,10017084,10017091,10017094,10017083,10017095,10017084,10017091,10017094,10017083,10017096,10017084,10017091,10017094,10017083,10017096,10017084,10017091,10017094,10017083,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017091,10017091,10017091,10017091,10017091,10017091,10017091</t>
+          <t>10017084,10048524,10017086,10048524,10017090,10017087,10017084,10048524,10017086,10048524,10017090,10017087,10017084,10048524,10017086,10048524,10017090,10017087,10017084,10048524,10017086,10048524,10017090,10017088,10017084,10017081,10017086,10017081,10017090,10017088,10017084,10017081,10017086,10017081,10017090,10017088,10017084,10017081,10017086,10017081,10017090,10017088,10017084,10017081,10017086,10017081,10017090,10017089,10017084,10048525,10017086,10048525,10017095,10017089,10017084,10048525,10017086,10048525,10017095,10017089,10017084,10048525,10017094,10048525,10017095,10017092,10017084,10048525,10017094,10048525,10017095,10017092,10017084,10017082,10017094,10017082,10017095,10017092,10017084,10017082,10017094,10017082,10017095,10017093,10017084,10017082,10017094,10017082,10017095,10017093,10017084,10017082,10017094,10017082,10017095,10017093,10017084,10017083,10017094,10017083,10017095,10017084,10017083,10017094,10017083,10017096,10017084,10017083,10017094,10017083,10017096,10017084,10017083,10017094,10017083,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017096,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017085,10017091,10017091,10017091,10017091,10017091,10017091,10017091,10017091</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L6 W23/25; N=168; EHP=17566.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x10,heavy:31x3,heavy:40x4,heavy:80x3,medium:83x8,swarm:84x47,heavy:86x3,heavy:88x3,fast:98x10,medium:108x9,medium:123x8</t>
+          <t>L6 W23/25; N=168; EHP=33756.753744; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:31x3,heavy:40x4,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017100,10017107,10017102,10048526,10017106,10017103,10017100,10017107,10017102,10048526,10017106,10017103,10017100,10017107,10017102,10048526,10017106,10017103,10017100,10017107,10017102,10048526,10017106,10017104,10017100,10017107,10017102,10048526,10017106,10017104,10017100,10017107,10017102,10017097,10017106,10017104,10017100,10017107,10017102,10017097,10017106,10017105,10017100,10017107,10017102,10017097,10017106,10017105,10017100,10017107,10017102,10017097,10017106,10017105,10017100,10017107,10017102,10048527,10017111,10017105,10017100,10017107,10017110,10048527,10017111,10017108,10017100,10017107,10017110,10048527,10017111,10017108,10017100,10017107,10017110,10048527,10017111,10017108,10017100,10017107,10017110,10017098,10017111,10017109,10017100,10017107,10017110,10017098,10017111,10017109,10017100,10017107,10017110,10017098,10017111,10017109,10017100,10017107,10017110,10017098,10017111,10017109,10017100,10017107,10017110,10017099,10017112,10017100,10017107,10017110,10017099,10017112,10017100,10017107,10017110,10017099,10017112,10017100,10017107,10017099,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017107,10017107,10017107,10017107,10017107,10017107</t>
+          <t>10017100,10048526,10017102,10048526,10017106,10017103,10017100,10048526,10017102,10048526,10017106,10017103,10017100,10048526,10017102,10048526,10017106,10017103,10017100,10048526,10017102,10048526,10017106,10017104,10017100,10048526,10017102,10048526,10017106,10017104,10017100,10017097,10017102,10017097,10017106,10017104,10017100,10017097,10017102,10017097,10017106,10017105,10017100,10017097,10017102,10017097,10017106,10017105,10017100,10017097,10017102,10017097,10017106,10017105,10017100,10048527,10017102,10048527,10017111,10017105,10017100,10048527,10017110,10048527,10017111,10017108,10017100,10048527,10017110,10048527,10017111,10017108,10017100,10048527,10017110,10048527,10017111,10017108,10017100,10017098,10017110,10017098,10017111,10017109,10017100,10017098,10017110,10017098,10017111,10017109,10017100,10017098,10017110,10017098,10017111,10017109,10017100,10017098,10017110,10017098,10017111,10017109,10017100,10017099,10017110,10017099,10017112,10017100,10017099,10017110,10017099,10017112,10017100,10017099,10017110,10017099,10017112,10017100,10017099,10017099,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017112,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017101,10017107,10017107,10017107,10017107,10017107,10017107,10017107</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L6 W24/25; N=174; EHP=18809.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x10,heavy:31x3,heavy:40x3,heavy:80x4,medium:83x9,swarm:84x48,heavy:86x3,heavy:88x4,fast:98x10,medium:108x8,medium:123x9</t>
+          <t>L6 W24/25; N=174; EHP=36149.314298; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:31x3,heavy:40x3,heavy:80x4,heavy:86x3,heavy:88x4,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017116,10017123,10017118,10048528,10017122,10017119,10017128,10017116,10017123,10017118,10048528,10017122,10017119,10017116,10017123,10017118,10048528,10017122,10017119,10017116,10017123,10017118,10048528,10017122,10017119,10017116,10017123,10017118,10017113,10017122,10017120,10017116,10017123,10017118,10017113,10017122,10017120,10017116,10017123,10017118,10017113,10017122,10017120,10017116,10017123,10017118,10017113,10017122,10017121,10017116,10017123,10017118,10017113,10017122,10017121,10017116,10017123,10017118,10048529,10017127,10017121,10017116,10017123,10017126,10048529,10017127,10017121,10017116,10017123,10017126,10048529,10017127,10017124,10017116,10017123,10017126,10048529,10017127,10017124,10017116,10017123,10017126,10017114,10017127,10017124,10017116,10017123,10017126,10017114,10017127,10017124,10017116,10017123,10017126,10017114,10017127,10017125,10017116,10017123,10017126,10017114,10017127,10017125,10017116,10017123,10017126,10017114,10017127,10017125,10017116,10017123,10017126,10017115,10017129,10017116,10017123,10017126,10017115,10017129,10017116,10017123,10017126,10017115,10017129,10017117,10017123,10017115,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123</t>
+          <t>10017116,10048528,10017118,10048528,10017122,10017119,10017128,10017116,10048528,10017118,10048528,10017122,10017119,10017116,10048528,10017118,10048528,10017122,10017119,10017116,10048528,10017118,10048528,10017122,10017119,10017116,10017113,10017118,10017113,10017122,10017120,10017116,10017113,10017118,10017113,10017122,10017120,10017116,10017113,10017118,10017113,10017122,10017120,10017116,10017113,10017118,10017113,10017122,10017121,10017116,10017113,10017118,10017113,10017122,10017121,10017116,10048529,10017118,10048529,10017127,10017121,10017116,10048529,10017126,10048529,10017127,10017121,10017116,10048529,10017126,10048529,10017127,10017124,10017116,10048529,10017126,10048529,10017127,10017124,10017116,10017114,10017126,10017114,10017127,10017124,10017116,10017114,10017126,10017114,10017127,10017124,10017116,10017114,10017126,10017114,10017127,10017125,10017116,10017114,10017126,10017114,10017127,10017125,10017116,10017114,10017126,10017114,10017127,10017125,10017116,10017115,10017126,10017115,10017129,10017116,10017115,10017126,10017115,10017129,10017116,10017115,10017126,10017115,10017129,10017117,10017115,10017115,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017129,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017117,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123,10017123</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L6 W25/25; N=180; EHP=37549.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x20,fast:30x10,heavy:31x4,heavy:40x3,heavy:80x4,medium:83x9,swarm:84x50,heavy:86x4,heavy:88x3,fast:98x11,medium:108x9,elite:123x1,medium:123x9</t>
+          <t>L6 W25/25; N=180; EHP=72158.814329; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x10,fast:98x11,heavy:31x4,heavy:40x3,heavy:80x4,heavy:86x4,heavy:88x3,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x20,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L06/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L06/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
